--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -981,7 +981,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>maria@empresa.com</t>
+          <t>mario@empresa.com</t>
         </is>
       </c>
       <c r="E161" t="n">

--- a/data/ventas.xlsx
+++ b/data/ventas.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -606,7 +606,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -756,7 +756,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -981,7 +981,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ana@empresa.com</t>
+          <t>hugo@empresa.com</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>mario@empresa.com</t>
+          <t>maria@empresa.com</t>
         </is>
       </c>
       <c r="E161" t="n">
